--- a/SALT/salt_mlip_grades.xlsx
+++ b/SALT/salt_mlip_grades.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB07204C-38E8-9B4B-9504-C1861625AA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F3BAB2-0C71-B64A-BEB7-152651B547FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10620" yWindow="1380" windowWidth="28040" windowHeight="18000" xr2:uid="{E23F5C05-CFF3-2C43-92A3-DE3C4CC8D611}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
